--- a/xlsx/Power/p5.xlsx
+++ b/xlsx/Power/p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C6EC5E-8FD4-4464-A41E-1F8F9BA35BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCF11D2-0B11-4470-9E18-85E38B3ED755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{82AB3B4B-FE31-4CB3-8484-9FB4E980CB64}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{82AB3B4B-FE31-4CB3-8484-9FB4E980CB64}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="C1">
-        <v>0.46</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="D1">
-        <v>0.58499999999999996</v>
+        <v>0.249</v>
       </c>
       <c r="E1">
-        <v>0.69799999999999995</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="F1">
-        <v>0.75600000000000001</v>
+        <v>0.55900000000000005</v>
       </c>
       <c r="G1">
-        <v>0.84299999999999997</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="H1">
-        <v>0.88400000000000001</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="I1">
-        <v>0.91200000000000003</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="J1">
-        <v>0.94399999999999995</v>
+        <v>0.90400000000000003</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.317</v>
       </c>
       <c r="C2">
-        <v>0.435</v>
+        <v>0.09</v>
       </c>
       <c r="D2">
-        <v>0.55300000000000005</v>
+        <v>0.252</v>
       </c>
       <c r="E2">
-        <v>0.67100000000000004</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="F2">
-        <v>0.73399999999999999</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="G2">
-        <v>0.82599999999999996</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="H2">
-        <v>0.871</v>
+        <v>0.78</v>
       </c>
       <c r="I2">
-        <v>0.9</v>
+        <v>0.82899999999999996</v>
       </c>
       <c r="J2">
-        <v>0.93700000000000006</v>
+        <v>0.89400000000000002</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="C3">
-        <v>0.374</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="D3">
-        <v>0.503</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="E3">
-        <v>0.59199999999999997</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="F3">
-        <v>0.66800000000000004</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="G3">
         <v>0.74</v>
       </c>
       <c r="H3">
-        <v>0.81100000000000005</v>
+        <v>0.81599999999999995</v>
       </c>
       <c r="I3">
-        <v>0.86</v>
+        <v>0.86099999999999999</v>
       </c>
       <c r="J3">
-        <v>0.89200000000000002</v>
+        <v>0.89500000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.129</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="B4">
-        <v>0.23799999999999999</v>
+        <v>0.253</v>
       </c>
       <c r="C4">
-        <v>0.33400000000000002</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="D4">
-        <v>0.46899999999999997</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="E4">
-        <v>0.54100000000000004</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="F4">
-        <v>0.61</v>
+        <v>0.61299999999999999</v>
       </c>
       <c r="G4">
         <v>0.67600000000000005</v>
       </c>
       <c r="H4">
-        <v>0.755</v>
+        <v>0.753</v>
       </c>
       <c r="I4">
         <v>0.80600000000000005</v>
       </c>
       <c r="J4">
-        <v>0.84499999999999997</v>
+        <v>0.84799999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>0.312</v>
       </c>
       <c r="C5">
-        <v>0.433</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D5">
-        <v>0.54700000000000004</v>
+        <v>0.129</v>
       </c>
       <c r="E5">
-        <v>0.70699999999999996</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="F5">
-        <v>0.73899999999999999</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="G5">
-        <v>0.81699999999999995</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="H5">
-        <v>0.85899999999999999</v>
+        <v>0.70599999999999996</v>
       </c>
       <c r="I5">
-        <v>0.91</v>
+        <v>0.79700000000000004</v>
       </c>
       <c r="J5">
-        <v>0.93300000000000005</v>
+        <v>0.84599999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.29499999999999998</v>
       </c>
       <c r="C6">
-        <v>0.42</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="D6">
-        <v>0.504</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="E6">
-        <v>0.61799999999999999</v>
+        <v>0.65400000000000003</v>
       </c>
       <c r="F6">
-        <v>0.68100000000000005</v>
+        <v>0.69899999999999995</v>
       </c>
       <c r="G6">
-        <v>0.78800000000000003</v>
+        <v>0.80100000000000005</v>
       </c>
       <c r="H6">
-        <v>0.83599999999999997</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="I6">
-        <v>0.876</v>
+        <v>0.88700000000000001</v>
       </c>
       <c r="J6">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.28299999999999997</v>
       </c>
       <c r="C7">
-        <v>0.38800000000000001</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="D7">
-        <v>0.48</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="E7">
-        <v>0.58599999999999997</v>
+        <v>0.58699999999999997</v>
       </c>
       <c r="F7">
-        <v>0.63700000000000001</v>
+        <v>0.63400000000000001</v>
       </c>
       <c r="G7">
-        <v>0.75600000000000001</v>
+        <v>0.748</v>
       </c>
       <c r="H7">
-        <v>0.80500000000000005</v>
+        <v>0.80600000000000005</v>
       </c>
       <c r="I7">
-        <v>0.84099999999999997</v>
+        <v>0.83899999999999997</v>
       </c>
       <c r="J7">
-        <v>0.89500000000000002</v>
+        <v>0.89300000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.17899999999999999</v>
       </c>
       <c r="C8">
-        <v>0.25700000000000001</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.33100000000000002</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="E8">
-        <v>0.40699999999999997</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="F8">
-        <v>0.45300000000000001</v>
+        <v>0.245</v>
       </c>
       <c r="G8">
-        <v>0.51400000000000001</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="H8">
-        <v>0.58299999999999996</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="I8">
-        <v>0.67700000000000005</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="J8">
-        <v>0.73799999999999999</v>
+        <v>0.25600000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="C9">
-        <v>0.14000000000000001</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="D9">
-        <v>0.14499999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="E9">
-        <v>0.221</v>
+        <v>0.70599999999999996</v>
       </c>
       <c r="F9">
-        <v>0.24399999999999999</v>
+        <v>0.376</v>
       </c>
       <c r="G9">
-        <v>0.26700000000000002</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="H9">
-        <v>0.35299999999999998</v>
+        <v>0.4</v>
       </c>
       <c r="I9">
-        <v>0.374</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="J9">
-        <v>0.433</v>
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p5.xlsx
+++ b/xlsx/Power/p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCF11D2-0B11-4470-9E18-85E38B3ED755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7124D3-B341-4C4C-A6A2-FC7BA2662A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{82AB3B4B-FE31-4CB3-8484-9FB4E980CB64}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{82AB3B4B-FE31-4CB3-8484-9FB4E980CB64}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="C1">
-        <v>8.2000000000000003E-2</v>
+        <v>0.46</v>
       </c>
       <c r="D1">
-        <v>0.249</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="E1">
-        <v>0.42199999999999999</v>
+        <v>0.69799999999999995</v>
       </c>
       <c r="F1">
-        <v>0.55900000000000005</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="G1">
-        <v>0.69399999999999995</v>
+        <v>0.84299999999999997</v>
       </c>
       <c r="H1">
-        <v>0.79400000000000004</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="I1">
-        <v>0.84099999999999997</v>
+        <v>0.91200000000000003</v>
       </c>
       <c r="J1">
-        <v>0.90400000000000003</v>
+        <v>0.94399999999999995</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.317</v>
       </c>
       <c r="C2">
-        <v>0.09</v>
+        <v>0.435</v>
       </c>
       <c r="D2">
-        <v>0.252</v>
+        <v>0.55300000000000005</v>
       </c>
       <c r="E2">
-        <v>0.42399999999999999</v>
+        <v>0.67100000000000004</v>
       </c>
       <c r="F2">
-        <v>0.54700000000000004</v>
+        <v>0.73399999999999999</v>
       </c>
       <c r="G2">
-        <v>0.68200000000000005</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="H2">
-        <v>0.78</v>
+        <v>0.871</v>
       </c>
       <c r="I2">
-        <v>0.82899999999999996</v>
+        <v>0.9</v>
       </c>
       <c r="J2">
-        <v>0.89400000000000002</v>
+        <v>0.93700000000000006</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="C3">
-        <v>0.42199999999999999</v>
+        <v>0.373</v>
       </c>
       <c r="D3">
-        <v>0.51200000000000001</v>
+        <v>0.503</v>
       </c>
       <c r="E3">
-        <v>0.60099999999999998</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="F3">
-        <v>0.67500000000000004</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="G3">
         <v>0.74</v>
       </c>
       <c r="H3">
-        <v>0.81599999999999995</v>
+        <v>0.81100000000000005</v>
       </c>
       <c r="I3">
-        <v>0.86099999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="J3">
-        <v>0.89500000000000002</v>
+        <v>0.89200000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.14299999999999999</v>
+        <v>0.129</v>
       </c>
       <c r="B4">
-        <v>0.253</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="C4">
-        <v>0.34100000000000003</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="D4">
-        <v>0.46400000000000002</v>
+        <v>0.46899999999999997</v>
       </c>
       <c r="E4">
-        <v>0.54200000000000004</v>
+        <v>0.54100000000000004</v>
       </c>
       <c r="F4">
-        <v>0.61299999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="G4">
         <v>0.67600000000000005</v>
       </c>
       <c r="H4">
-        <v>0.753</v>
+        <v>0.755</v>
       </c>
       <c r="I4">
         <v>0.80600000000000005</v>
       </c>
       <c r="J4">
-        <v>0.84799999999999998</v>
+        <v>0.84499999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>0.312</v>
       </c>
       <c r="C5">
-        <v>1.4999999999999999E-2</v>
+        <v>0.433</v>
       </c>
       <c r="D5">
-        <v>0.129</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="E5">
-        <v>0.28899999999999998</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="F5">
-        <v>0.47199999999999998</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="G5">
-        <v>0.60099999999999998</v>
+        <v>0.81699999999999995</v>
       </c>
       <c r="H5">
-        <v>0.70599999999999996</v>
+        <v>0.85899999999999999</v>
       </c>
       <c r="I5">
-        <v>0.79700000000000004</v>
+        <v>0.91</v>
       </c>
       <c r="J5">
-        <v>0.84599999999999997</v>
+        <v>0.93300000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -561,31 +561,31 @@
         <v>0.155</v>
       </c>
       <c r="B6">
-        <v>0.29499999999999998</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="C6">
-        <v>0.57599999999999996</v>
+        <v>0.42</v>
       </c>
       <c r="D6">
-        <v>0.58299999999999996</v>
+        <v>0.504</v>
       </c>
       <c r="E6">
-        <v>0.65400000000000003</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="F6">
-        <v>0.69899999999999995</v>
+        <v>0.68100000000000005</v>
       </c>
       <c r="G6">
-        <v>0.80100000000000005</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="H6">
-        <v>0.84799999999999998</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="I6">
-        <v>0.88700000000000001</v>
+        <v>0.876</v>
       </c>
       <c r="J6">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.28299999999999997</v>
       </c>
       <c r="C7">
-        <v>0.38100000000000001</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="D7">
-        <v>0.47799999999999998</v>
+        <v>0.48</v>
       </c>
       <c r="E7">
-        <v>0.58699999999999997</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="F7">
-        <v>0.63400000000000001</v>
+        <v>0.63700000000000001</v>
       </c>
       <c r="G7">
-        <v>0.748</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="H7">
-        <v>0.80600000000000005</v>
+        <v>0.80500000000000005</v>
       </c>
       <c r="I7">
-        <v>0.83899999999999997</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="J7">
-        <v>0.89300000000000002</v>
+        <v>0.89500000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.17899999999999999</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="D8">
-        <v>6.5000000000000002E-2</v>
+        <v>0.33100000000000002</v>
       </c>
       <c r="E8">
-        <v>0.13500000000000001</v>
+        <v>0.40699999999999997</v>
       </c>
       <c r="F8">
-        <v>0.245</v>
+        <v>0.45300000000000001</v>
       </c>
       <c r="G8">
-        <v>0.33800000000000002</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="H8">
-        <v>0.40300000000000002</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="I8">
-        <v>0.23699999999999999</v>
+        <v>0.67700000000000005</v>
       </c>
       <c r="J8">
-        <v>0.25600000000000001</v>
+        <v>0.73799999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="C9">
-        <v>0.41299999999999998</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D9">
-        <v>0.9</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="E9">
-        <v>0.70599999999999996</v>
+        <v>0.221</v>
       </c>
       <c r="F9">
-        <v>0.376</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="G9">
-        <v>0.34399999999999997</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="H9">
-        <v>0.4</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="I9">
-        <v>0.40400000000000003</v>
+        <v>0.374</v>
       </c>
       <c r="J9">
-        <v>0.45</v>
+        <v>0.433</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p5.xlsx
+++ b/xlsx/Power/p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7124D3-B341-4C4C-A6A2-FC7BA2662A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5519030-EE49-4448-B7BC-80892AA986D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{82AB3B4B-FE31-4CB3-8484-9FB4E980CB64}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{82AB3B4B-FE31-4CB3-8484-9FB4E980CB64}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,7 +398,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.15</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="B1">
         <v>0.32500000000000001</v>
@@ -407,13 +407,13 @@
         <v>0.46</v>
       </c>
       <c r="D1">
-        <v>0.58499999999999996</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="E1">
-        <v>0.69799999999999995</v>
+        <v>0.7</v>
       </c>
       <c r="F1">
-        <v>0.75600000000000001</v>
+        <v>0.75800000000000001</v>
       </c>
       <c r="G1">
         <v>0.84299999999999997</v>
@@ -422,74 +422,74 @@
         <v>0.88400000000000001</v>
       </c>
       <c r="I1">
-        <v>0.91200000000000003</v>
+        <v>0.91400000000000003</v>
       </c>
       <c r="J1">
-        <v>0.94399999999999995</v>
+        <v>0.94499999999999995</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.151</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="B2">
-        <v>0.317</v>
+        <v>0.318</v>
       </c>
       <c r="C2">
         <v>0.435</v>
       </c>
       <c r="D2">
-        <v>0.55300000000000005</v>
+        <v>0.55200000000000005</v>
       </c>
       <c r="E2">
-        <v>0.67100000000000004</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="F2">
         <v>0.73399999999999999</v>
       </c>
       <c r="G2">
-        <v>0.82599999999999996</v>
+        <v>0.82099999999999995</v>
       </c>
       <c r="H2">
-        <v>0.871</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="I2">
-        <v>0.9</v>
+        <v>0.90300000000000002</v>
       </c>
       <c r="J2">
-        <v>0.93700000000000006</v>
+        <v>0.93799999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.13400000000000001</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="B3">
-        <v>0.26700000000000002</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="C3">
-        <v>0.373</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="D3">
         <v>0.503</v>
       </c>
       <c r="E3">
-        <v>0.59199999999999997</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="F3">
-        <v>0.66800000000000004</v>
+        <v>0.67100000000000004</v>
       </c>
       <c r="G3">
-        <v>0.74</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="H3">
-        <v>0.81100000000000005</v>
+        <v>0.81899999999999995</v>
       </c>
       <c r="I3">
-        <v>0.86</v>
+        <v>0.86099999999999999</v>
       </c>
       <c r="J3">
-        <v>0.89200000000000002</v>
+        <v>0.90100000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -497,127 +497,127 @@
         <v>0.129</v>
       </c>
       <c r="B4">
-        <v>0.23799999999999999</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="C4">
-        <v>0.33400000000000002</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="D4">
-        <v>0.46899999999999997</v>
+        <v>0.47</v>
       </c>
       <c r="E4">
-        <v>0.54100000000000004</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="F4">
-        <v>0.61</v>
+        <v>0.61299999999999999</v>
       </c>
       <c r="G4">
-        <v>0.67600000000000005</v>
+        <v>0.67700000000000005</v>
       </c>
       <c r="H4">
-        <v>0.755</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="I4">
-        <v>0.80600000000000005</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="J4">
-        <v>0.84499999999999997</v>
+        <v>0.85299999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.17699999999999999</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>0.312</v>
+        <v>2E-3</v>
       </c>
       <c r="C5">
-        <v>0.433</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="D5">
-        <v>0.54700000000000004</v>
+        <v>1.4E-2</v>
       </c>
       <c r="E5">
-        <v>0.70699999999999996</v>
+        <v>1.9E-2</v>
       </c>
       <c r="F5">
-        <v>0.73899999999999999</v>
+        <v>4.7E-2</v>
       </c>
       <c r="G5">
-        <v>0.81699999999999995</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="H5">
-        <v>0.85899999999999999</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="I5">
-        <v>0.91</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="J5">
-        <v>0.93300000000000005</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.155</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="B6">
-        <v>0.29399999999999998</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="C6">
-        <v>0.42</v>
+        <v>0.41899999999999998</v>
       </c>
       <c r="D6">
         <v>0.504</v>
       </c>
       <c r="E6">
-        <v>0.61799999999999999</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="F6">
-        <v>0.68100000000000005</v>
+        <v>0.67900000000000005</v>
       </c>
       <c r="G6">
-        <v>0.78800000000000003</v>
+        <v>0.78400000000000003</v>
       </c>
       <c r="H6">
-        <v>0.83599999999999997</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="I6">
-        <v>0.876</v>
+        <v>0.873</v>
       </c>
       <c r="J6">
-        <v>0.91</v>
+        <v>0.91300000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.14899999999999999</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="B7">
-        <v>0.28299999999999997</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="C7">
-        <v>0.38800000000000001</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="D7">
-        <v>0.48</v>
+        <v>0.47599999999999998</v>
       </c>
       <c r="E7">
         <v>0.58599999999999997</v>
       </c>
       <c r="F7">
-        <v>0.63700000000000001</v>
+        <v>0.63500000000000001</v>
       </c>
       <c r="G7">
-        <v>0.75600000000000001</v>
+        <v>0.754</v>
       </c>
       <c r="H7">
-        <v>0.80500000000000005</v>
+        <v>0.80600000000000005</v>
       </c>
       <c r="I7">
         <v>0.84099999999999997</v>
       </c>
       <c r="J7">
-        <v>0.89500000000000002</v>
+        <v>0.89300000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -631,10 +631,10 @@
         <v>0.25700000000000001</v>
       </c>
       <c r="D8">
-        <v>0.33100000000000002</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="E8">
-        <v>0.40699999999999997</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="F8">
         <v>0.45300000000000001</v>
@@ -643,7 +643,7 @@
         <v>0.51400000000000001</v>
       </c>
       <c r="H8">
-        <v>0.58299999999999996</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="I8">
         <v>0.67700000000000005</v>
@@ -654,34 +654,34 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>0.109</v>
+        <v>0.111</v>
       </c>
       <c r="B9">
-        <v>0.16300000000000001</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="C9">
         <v>0.14000000000000001</v>
       </c>
       <c r="D9">
-        <v>0.14499999999999999</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="E9">
         <v>0.221</v>
       </c>
       <c r="F9">
-        <v>0.24399999999999999</v>
+        <v>0.246</v>
       </c>
       <c r="G9">
-        <v>0.26700000000000002</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="H9">
-        <v>0.35299999999999998</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="I9">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="J9">
-        <v>0.433</v>
+        <v>0.439</v>
       </c>
     </row>
   </sheetData>
